--- a/artfynd/A 43942-2024 artfynd.xlsx
+++ b/artfynd/A 43942-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>89557379</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398316.1096504302</v>
+        <v>398316</v>
       </c>
       <c r="R2" t="n">
-        <v>7081551.793996869</v>
+        <v>7081552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89557403</v>
+        <v>89557375</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398350.8274355286</v>
+        <v>398363</v>
       </c>
       <c r="R3" t="n">
-        <v>7081559.057574219</v>
+        <v>7081546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89557383</v>
+        <v>89557403</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397895.8896890822</v>
+        <v>398351</v>
       </c>
       <c r="R4" t="n">
-        <v>7081096.084269379</v>
+        <v>7081559</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89557368</v>
+        <v>89557383</v>
       </c>
       <c r="B5" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397902.0987459304</v>
+        <v>397896</v>
       </c>
       <c r="R5" t="n">
-        <v>7081083.076607384</v>
+        <v>7081096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89557375</v>
+        <v>89557368</v>
       </c>
       <c r="B6" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1841</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398362.7784048849</v>
+        <v>397902</v>
       </c>
       <c r="R6" t="n">
-        <v>7081545.86677689</v>
+        <v>7081083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89557399</v>
+        <v>89567841</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398242.0588966428</v>
+        <v>397723</v>
       </c>
       <c r="R7" t="n">
-        <v>7081544.923208084</v>
+        <v>7080952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43942-2024 artfynd.xlsx
+++ b/artfynd/A 43942-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557368</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557379</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557375</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>